--- a/sensor_history.xlsx
+++ b/sensor_history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,9 +468,78 @@
         <v>Optimal Freshness</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4">
+        <v>1784101512508</v>
+      </c>
+      <c r="B4" t="str">
+        <v>15/07/2026, 1:15:12 PM</v>
+      </c>
+      <c r="C4" t="str">
+        <v>29.5</v>
+      </c>
+      <c r="D4">
+        <v>99</v>
+      </c>
+      <c r="E4">
+        <v>600</v>
+      </c>
+      <c r="F4" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1784101512508</v>
+      </c>
+      <c r="B5" t="str">
+        <v>15/07/2026, 1:15:12 PM</v>
+      </c>
+      <c r="C5" t="str">
+        <v>29.5</v>
+      </c>
+      <c r="D5">
+        <v>99</v>
+      </c>
+      <c r="E5">
+        <v>600</v>
+      </c>
+      <c r="F5" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1784102169761</v>
+      </c>
+      <c r="B6" t="str">
+        <v>15/07/2026, 1:26:09 PM</v>
+      </c>
+      <c r="C6" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="D6">
+        <v>86</v>
+      </c>
+      <c r="E6">
+        <v>90</v>
+      </c>
+      <c r="F6" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Optimal Freshness</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sensor_history.xlsx
+++ b/sensor_history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -537,9 +537,101 @@
         <v>Optimal Freshness</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>1784104307071</v>
+      </c>
+      <c r="B7" t="str">
+        <v>15/07/2026, 2:01:47 PM</v>
+      </c>
+      <c r="C7" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="D7">
+        <v>98</v>
+      </c>
+      <c r="E7">
+        <v>420</v>
+      </c>
+      <c r="F7" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1784107908497</v>
+      </c>
+      <c r="B8" t="str">
+        <v>15/07/2026, 3:01:48 PM</v>
+      </c>
+      <c r="C8" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="D8">
+        <v>85</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Optimal Freshness</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1784108310164</v>
+      </c>
+      <c r="B9" t="str">
+        <v>15/07/2026, 3:08:30 PM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="D9">
+        <v>98</v>
+      </c>
+      <c r="E9">
+        <v>420</v>
+      </c>
+      <c r="F9" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1784108310164</v>
+      </c>
+      <c r="B10" t="str">
+        <v>15/07/2026, 3:08:30 PM</v>
+      </c>
+      <c r="C10" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="D10">
+        <v>98</v>
+      </c>
+      <c r="E10">
+        <v>420</v>
+      </c>
+      <c r="F10" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sensor_history.xlsx
+++ b/sensor_history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -629,9 +629,101 @@
         <v>Spoilage / Toxic Risk</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>1784108784407</v>
+      </c>
+      <c r="B11" t="str">
+        <v>15/07/2026, 3:16:24 PM</v>
+      </c>
+      <c r="C11" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="D11">
+        <v>86</v>
+      </c>
+      <c r="E11">
+        <v>90</v>
+      </c>
+      <c r="F11" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Optimal Freshness</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1784111391304</v>
+      </c>
+      <c r="B12" t="str">
+        <v>15/07/2026, 3:59:51 PM</v>
+      </c>
+      <c r="C12" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="D12">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>320</v>
+      </c>
+      <c r="F12" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Ripening / Monitor</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1784565921118</v>
+      </c>
+      <c r="B13" t="str">
+        <v>20/07/2026, 10:15:21 PM</v>
+      </c>
+      <c r="C13" t="str">
+        <v>19.5</v>
+      </c>
+      <c r="D13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>490</v>
+      </c>
+      <c r="F13" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1784565921118</v>
+      </c>
+      <c r="B14" t="str">
+        <v>20/07/2026, 10:15:21 PM</v>
+      </c>
+      <c r="C14" t="str">
+        <v>19.5</v>
+      </c>
+      <c r="D14">
+        <v>74</v>
+      </c>
+      <c r="E14">
+        <v>490</v>
+      </c>
+      <c r="F14" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
 </worksheet>
 </file>